--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570113907</v>
+        <v>46157.93105218939</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105218939</v>
+        <v>46157.93176221813</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176221813</v>
+        <v>46157.93401627245</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401627245</v>
+        <v>46157.93719633041</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719633041</v>
+        <v>46158.28217766289</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217766289</v>
+        <v>46158.2968392621</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2968392621</v>
+        <v>46158.29816676882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29816676882</v>
+        <v>46158.33388871101</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388871101</v>
+        <v>46158.36858630807</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858630807</v>
+        <v>46158.37289349668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
